--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,35 +483,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -528,35 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -618,11 +618,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -663,40 +663,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: PANW)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -708,40 +708,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NMM</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: ECO)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -753,11 +753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -766,27 +766,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-teekay-tankers-tnk.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -798,35 +798,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-charles-schwab-schw.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,40 +888,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>URGN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: IOVA)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -933,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -961,12 +961,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CDNA)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,40 +1023,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permian-resources-pr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: PR)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1068,35 +1068,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,40 +1113,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 59</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1158,40 +1158,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 33</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: AAPL)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1356,22 +1356,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>DELL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>CRCT</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cricut-cl-a-crct.htm</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CRCT)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1383,40 +1383,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>NPSCY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-nippon-steel-adr-npscy.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>OPLN</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-openlane-opln.htm</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>PAG</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: OPLN)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1473,40 +1473,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apa-apa.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CRVL)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1518,35 +1518,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 69</t>
+          <t>▲ 31</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1563,35 +1563,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-banco-bilbao-vizcaya-argentaria-adr-bbva.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,35 +1608,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-remitly-global-rely.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1653,35 +1653,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-charles-schwab-schw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1698,40 +1698,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-remitly-global-rely.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WEX</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: RELY)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1743,40 +1743,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 34</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1788,35 +1788,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1833,40 +1833,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 41</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: HLP)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1878,35 +1878,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1923,35 +1923,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 52</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-reinsurance-group-of-america-rga.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1968,40 +1968,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-banco-bilbao-vizcaya-argentaria-adr-bbva.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ISNPY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: BBVA)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: BMY)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2058,35 +2058,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2103,40 +2103,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: NVDA)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2148,40 +2148,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>NHC</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: AVAH)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2193,35 +2193,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 43</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2238,35 +2238,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-williamssonoma-wsm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 26</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2296,22 +2296,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,35 +2373,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 30</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 43</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2431,22 +2431,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2463,35 +2463,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2508,40 +2508,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-reinsurance-group-of-america-rga.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: RGA)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2553,40 +2553,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 33</t>
+          <t>▲ 25</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2598,40 +2598,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▼ 24</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-europacific-partners-ccep.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CCEP)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2661,22 +2661,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>CPAY</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>VIRT</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-virtu-financial-virt.htm</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: VIRT)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2688,40 +2688,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: UI)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2733,40 +2733,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-welltower-well.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-europacific-partners-ccep.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: WELL)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2778,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2823,40 +2823,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▲ 49</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: MCK)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2868,35 +2868,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2913,40 +2913,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2958,35 +2958,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 37</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3003,40 +3003,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 39</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: ERO)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3048,35 +3048,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3093,40 +3093,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 27</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-roper-technologies-rop.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: ROP)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3138,35 +3138,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,40 +3183,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 42</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: TAL)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3228,40 +3228,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-welltower-well.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: YAHOY)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3273,40 +3273,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ase-technology-holding-adr-asx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-adobe-adbe.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: ASX)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3318,35 +3318,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3363,35 +3363,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 32</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3408,40 +3408,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CSW</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: MTW)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3453,35 +3453,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3498,35 +3498,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 48</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ssr-mining-ssrm.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3543,35 +3543,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3588,40 +3588,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▲ 32</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: KEYS)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3633,35 +3633,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3678,40 +3678,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 33</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elastic-estc.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: SBFG)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3723,40 +3723,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 28</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: NTRS)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3768,35 +3768,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3813,35 +3813,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 31</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3858,35 +3858,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 35</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3903,35 +3903,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dexcom-dxcm.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3948,40 +3948,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3993,40 +3993,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 50</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: TWIN)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4038,11 +4038,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4051,22 +4051,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-intapp-inta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4128,40 +4128,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ww-grainger-gww.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-intapp-inta.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: GWW)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4173,40 +4173,40 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▼ 48</t>
+          <t>▲ 31</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SGHC</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-super-group-sghc-sghc.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4218,40 +4218,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-republic-services-rsg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>TTEK</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: RSG)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4263,35 +4263,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▲ 29</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4308,35 +4308,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4353,40 +4353,40 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-clean-harbors-clh.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4398,11 +4398,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▲ 34</t>
+          <t>▼ 28</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4411,22 +4411,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4443,35 +4443,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4488,35 +4488,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ww-grainger-gww.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4533,40 +4533,40 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 32</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-north-european-oil-royalty-trust-nrt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: NRT)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4578,40 +4578,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 48</t>
+          <t>▲ 36</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ssr-mining-ssrm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: SSRM)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4623,40 +4623,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NVZMY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-novonesis-adr-nvzmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: NVZMY)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4668,33 +4668,35 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>▲ 3</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>97</v>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4711,11 +4713,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -4724,22 +4726,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tenet-healthcare-thc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dexcom-dxcm.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4756,40 +4758,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: SZKMY)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4801,40 +4803,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: XMTR)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4846,40 +4848,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▲ 31</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ICAGY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4891,40 +4893,40 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-healthstream-hstm.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4936,35 +4938,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4981,40 +4983,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CAAS)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5026,35 +5028,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 24</t>
+          <t>▲ 30</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5071,40 +5073,40 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SENEB</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CHEF)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5116,40 +5118,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▼ 38</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: MATV)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5161,40 +5163,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: BOX)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5206,40 +5208,40 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▼ 37</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5251,35 +5253,35 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 39</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5296,40 +5298,40 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: MLAB)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5341,35 +5343,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>NVZMY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-novonesis-adr-nvzmy.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>NVZMY</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5386,40 +5388,40 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▼ 37</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: AER)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5431,40 +5433,40 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sonotek-sotk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: SOTK)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5476,35 +5478,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5521,35 +5523,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5566,35 +5568,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 44</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5611,35 +5613,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5656,35 +5658,35 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 28</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5701,40 +5703,40 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 29</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>MAMA</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-mamas-creations-mama.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CARG</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: MTCH)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5746,40 +5748,40 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>SENEB</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-american-states-water-awr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-seneca-foods-cl-b-seneb.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5791,40 +5793,40 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>IDEXY</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: ANF)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5836,35 +5838,35 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5881,35 +5883,35 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▼ 30</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sps-commerce-spsc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-north-european-oil-royalty-trust-nrt.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5926,40 +5928,40 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ICAGY</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-international-consolidated-airlines-group-adr-icagy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: ICAGY)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5971,35 +5973,35 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-american-states-water-awr.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6016,35 +6018,35 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6061,40 +6063,40 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-target-tgt.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>SBGSY</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: OESX)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -6106,35 +6108,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sps-commerce-spsc.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6151,35 +6153,35 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6196,40 +6198,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>HURC</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: MTLS)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6241,40 +6243,40 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-sonotek-sotk.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: PRTS)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6286,11 +6288,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6331,40 +6333,40 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>RYCEY</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: NPK)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6376,35 +6378,35 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6421,40 +6423,40 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>RYCEY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-rollsroyce-holdings-adr-rycey.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -6466,35 +6468,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 24</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6511,35 +6513,35 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-murphy-usa-musa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6556,35 +6558,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6601,11 +6603,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -6614,27 +6616,27 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>SRGHY</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-shoprite-holdings-adr-srghy.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -6646,11 +6648,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -6674,12 +6676,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>USLM</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착: CPAC)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6691,35 +6693,35 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-frontdoor-ftdr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6731,40 +6733,40 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-frontdoor-ftdr.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6776,16 +6778,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -6821,35 +6823,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>135</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FIGS</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-figs-figs.htm</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>실패 (랭킹 영역을 찾을 수 없음)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -491,27 +491,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -528,35 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palantir-technologies-pltr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-teekay-tankers-tnk.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,35 +663,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,11 +753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -766,27 +766,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-teekay-tankers-tnk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -798,40 +798,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-charles-schwab-schw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -851,27 +851,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,40 +888,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,40 +1068,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1113,40 +1113,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 59</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1158,40 +1158,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 26</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,40 +1338,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1383,40 +1383,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NPSCY</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-nippon-steel-adr-npscy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1428,35 +1428,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>NPSCY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1473,35 +1473,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apa-apa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1518,35 +1518,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 31</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1571,27 +1571,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-banco-bilbao-vizcaya-argentaria-adr-bbva.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,35 +1608,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-remitly-global-rely.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1653,40 +1653,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1698,40 +1698,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 42</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1743,40 +1743,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-remitly-global-rely.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1788,35 +1788,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1833,40 +1833,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permian-resources-pr.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1878,35 +1878,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 33</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-reinsurance-group-of-america-rga.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1968,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2013,35 +2013,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-bristol-myers-squibb-bmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2071,22 +2071,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2103,35 +2103,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2148,35 +2148,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,35 +2193,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2238,40 +2238,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-business-financial-services-fbiz.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2283,35 +2283,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,35 +2373,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2426,32 +2426,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-bancorp-usb.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2463,35 +2463,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2508,35 +2508,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2553,40 +2553,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2598,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 24</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-reinsurance-group-of-america-rga.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>VIRT</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2688,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-bristol-myers-squibb-bmy.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,35 +2733,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 35</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-europacific-partners-ccep.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2778,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2823,35 +2823,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2868,35 +2868,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2913,40 +2913,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 23</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2958,35 +2958,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3003,35 +3003,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3048,35 +3048,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3093,40 +3093,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3138,35 +3138,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,35 +3183,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3228,40 +3228,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-welltower-well.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3273,35 +3273,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-adobe-adbe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-chemed-che.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3318,35 +3318,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3363,35 +3363,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3408,40 +3408,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3453,35 +3453,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3498,35 +3498,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ssr-mining-ssrm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3543,35 +3543,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3588,35 +3588,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▲ 32</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3628,40 +3628,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3673,40 +3673,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 33</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>NREF</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elastic-estc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nexpoint-real-estate-finance-nref.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3718,85 +3718,85 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 28</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3808,40 +3808,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,40 +3853,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3898,130 +3898,130 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4033,40 +4033,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4078,12 +4078,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4091,27 +4091,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4123,40 +4123,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-intapp-inta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4168,16 +4168,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 31</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -4191,17 +4191,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>EVVTY</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>SGHC</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-super-group-sghc-sghc.htm</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>EVVTY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4213,40 +4213,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 42</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-adobe-adbe.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4258,40 +4258,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▼ 35</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4303,1992 +4303,1992 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>CLH</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-clean-harbors-clh.htm</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>RSG</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>USFD</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>USFD</t>
-        </is>
-      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>FRD</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>GWW</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ww-grainger-gww.htm</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>GWW</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>CIX</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>CIX</t>
-        </is>
-      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▲ 36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>MTLS</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>MTLS</t>
-        </is>
-      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>JAPAY</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>JAPAY</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>XMTR</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>XMTR</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>DXCM</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dexcom-dxcm.htm</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>DXCM</t>
-        </is>
-      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>MTCH</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>MTCH</t>
-        </is>
-      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>ELF</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>ELF</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>JAPSY</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>ICAGY</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>HSTM</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-healthstream-hstm.htm</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>HURN</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>MATV</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>MATV</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>LILAK</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>LILAK</t>
-        </is>
-      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
           <t>AGM</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>AGM</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>LITE</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
           <t>BASFY</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>BASFY</t>
-        </is>
-      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
           <t>IMAX</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>IMAX</t>
-        </is>
-      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
           <t>NUTX</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>THC</t>
-        </is>
-      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
           <t>CRS</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>CRS</t>
-        </is>
-      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
           <t>NVZMY</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-novonesis-adr-nvzmy.htm</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>NVZMY</t>
-        </is>
-      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>JBHT</t>
-        </is>
-      </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
           <t>ESP</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>ESP</t>
-        </is>
-      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
           <t>VWDRY</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>VWDRY</t>
-        </is>
-      </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
           <t>LTH</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
           <t>AVNT</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>AVNT</t>
-        </is>
-      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
           <t>AER</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>AER</t>
-        </is>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
           <t>MLAB</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>MLAB</t>
-        </is>
-      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
           <t>MAMA</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-mamas-creations-mama.htm</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>TATYY</t>
-        </is>
-      </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
           <t>SENEB</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-seneca-foods-cl-b-seneb.htm</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>CHEF</t>
-        </is>
-      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>CHCI</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>CHCI</t>
-        </is>
-      </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
           <t>TILE</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-north-european-oil-royalty-trust-nrt.htm</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>NRT</t>
-        </is>
-      </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
           <t>OESX</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>OESX</t>
-        </is>
-      </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
           <t>AWR</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-american-states-water-awr.htm</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
           <t>EAT</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>EAT</t>
-        </is>
-      </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-target-tgt.htm</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>FIVE</t>
-        </is>
-      </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
           <t>SPSC</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sps-commerce-spsc.htm</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
           <t>ANF</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>ANF</t>
-        </is>
-      </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
           <t>ODC</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>ODC</t>
-        </is>
-      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
           <t>SOTK</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sonotek-sotk.htm</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -6296,359 +6296,359 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
           <t>XOS</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-xos-xos.htm</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>XOS</t>
-        </is>
-      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
           <t>HTHT</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>HTHT</t>
-        </is>
-      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
           <t>PRTS</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>PRTS</t>
-        </is>
-      </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
           <t>RYCEY</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-rollsroyce-holdings-adr-rycey.htm</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>NPK</t>
-        </is>
-      </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
           <t>IESC</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>IESC</t>
-        </is>
-      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
           <t>FSLR</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
           <t>SRGHY</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-shoprite-holdings-adr-srghy.htm</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>MUSA</t>
-        </is>
-      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6656,210 +6656,212 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
           <t>CPAC</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>CPAC</t>
-        </is>
-      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
           <t>GIC</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>GIC</t>
-        </is>
-      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
           <t>FTDR</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-frontdoor-ftdr.htm</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>FTDR</t>
-        </is>
-      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
           <t>HZO</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>HZO</t>
-        </is>
-      </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>142</v>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
           <t>FIGS</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-figs-figs.htm</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>JRSH</t>
-        </is>
-      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,11 +483,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -618,11 +618,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -663,11 +663,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -708,11 +708,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -753,11 +753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -826,12 +826,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,22 +901,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -933,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -946,22 +946,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,40 +1158,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,11 +1293,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1338,11 +1338,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NPSCY</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1473,11 +1473,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1518,11 +1518,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1563,11 +1563,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1653,40 +1653,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1698,35 +1698,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 42</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1788,11 +1788,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1833,11 +1833,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 33</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2148,35 +2148,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,35 +2193,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-business-financial-services-fbiz.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-business-financial-services-fbiz.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2283,35 +2283,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,35 +2373,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-bancorp-usb.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2418,40 +2418,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-bancorp-usb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2463,35 +2463,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2598,11 +2598,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2643,40 +2643,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-bristol-myers-squibb-bmy.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2688,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-bristol-myers-squibb-bmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2778,11 +2778,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2823,11 +2823,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2868,11 +2868,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2913,35 +2913,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2958,35 +2958,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3003,35 +3003,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3048,35 +3048,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3093,40 +3093,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3138,35 +3138,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,40 +3183,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3228,40 +3228,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3273,11 +3273,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3318,40 +3318,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3363,35 +3363,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3408,35 +3408,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3498,11 +3498,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3543,35 +3543,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>NREF</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nexpoint-real-estate-finance-nref.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>NREF</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3628,40 +3628,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3673,106 +3673,104 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 11</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>62</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NREF</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nexpoint-real-estate-finance-nref.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3808,40 +3806,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,40 +3851,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3898,85 +3896,81 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 16</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>65</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ww-grainger-gww.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▲ 1</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>85</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3988,40 +3982,38 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 8</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>77</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4033,40 +4025,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4078,40 +4070,38 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 10</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>78</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4123,40 +4113,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4168,85 +4158,83 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▼ 12</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>83</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SGHC</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▼ 42</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-adobe-adbe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4258,40 +4246,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4303,192 +4291,188 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>88</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>89</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4496,224 +4480,216 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>91</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>92</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>93</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>94</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4721,832 +4697,800 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>96</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>97</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>98</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>99</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>100</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-clean-harbors-clh.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>101</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>102</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>103</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-adobe-adbe.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>105</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>106</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>107</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>108</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-healthstream-hstm.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>NVZMY</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>110</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>111</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>112</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>113</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5556,132 +5500,128 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>115</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>XOS</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>116</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5691,312 +5631,298 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>117</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NVZMY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-novonesis-adr-nvzmy.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>MAMA</t>
+          <t>NVZMY</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>118</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>SENEB</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>119</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MAMA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-mamas-creations-mama.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MAMA</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>120</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>121</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>122</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SENEB</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-seneca-foods-cl-b-seneb.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>SENEB</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>123</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-excelerate-energy-ee.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6006,132 +5932,126 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>124</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>125</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>126</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sps-commerce-spsc.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6141,627 +6061,599 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>127</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-sonotek-sotk.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>128</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>129</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>130</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>XOS</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>131</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>132</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>133</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>RYCEY</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>134</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>135</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>136</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>137</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RYCEY</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-rollsroyce-holdings-adr-rycey.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>SRGHY</t>
+          <t>RYCEY</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>138</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SRGHY</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-shoprite-holdings-adr-srghy.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>SRGHY</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>139</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>140</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-frontdoor-ftdr.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6771,42 +6663,40 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>141</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6816,42 +6706,40 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>142</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6861,7 +6749,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -888,11 +888,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -933,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -978,11 +978,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2193,11 +2193,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2328,11 +2328,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2373,11 +2373,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2463,11 +2463,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2688,11 +2688,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2913,11 +2913,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2958,11 +2958,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3003,11 +3003,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3048,11 +3048,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3093,11 +3093,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3138,11 +3138,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3183,11 +3183,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3228,11 +3228,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3318,11 +3318,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3408,11 +3408,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3543,11 +3543,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3633,11 +3633,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3678,10 +3678,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>72</v>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>machine</t>
@@ -3721,11 +3723,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3766,11 +3768,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3811,11 +3813,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3901,10 +3903,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>77</v>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>retail</t>
@@ -3944,10 +3948,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>78</v>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>electrncs</t>
@@ -3987,10 +3993,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>79</v>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>electrncs</t>
@@ -4030,11 +4038,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4075,10 +4083,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>81</v>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>metals</t>
@@ -4118,11 +4128,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4163,10 +4173,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>83</v>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -4341,11 +4353,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4386,10 +4398,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>88</v>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>transportation</t>
@@ -4429,10 +4443,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>89</v>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>telecom</t>
@@ -4517,10 +4533,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>91</v>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>misc</t>
@@ -4560,10 +4578,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>92</v>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>telecom</t>
@@ -4603,10 +4623,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>93</v>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
           <t>transportation</t>
@@ -4646,10 +4668,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>94</v>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>medical</t>
@@ -4672,12 +4696,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4734,10 +4758,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>96</v>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -4777,10 +4803,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>97</v>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>food/bev</t>
@@ -4820,10 +4848,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>98</v>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>metals</t>
@@ -4863,10 +4893,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>99</v>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>finance</t>
@@ -4906,10 +4938,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>100</v>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>machine</t>
@@ -4949,10 +4983,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>101</v>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>energy</t>
@@ -4992,10 +5028,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>102</v>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>chemical</t>
@@ -5035,10 +5073,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>103</v>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>machine</t>
@@ -5078,11 +5118,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -5123,10 +5163,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>105</v>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>real est</t>
@@ -5166,10 +5208,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>106</v>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>finance</t>
@@ -5209,10 +5253,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>107</v>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>internet</t>
@@ -5252,10 +5298,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>108</v>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>busins svc</t>
@@ -5295,11 +5343,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -5340,10 +5388,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>110</v>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>building</t>
@@ -5383,10 +5433,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>111</v>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>medical</t>
@@ -5426,10 +5478,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>112</v>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>alcohl/tob/thc</t>
@@ -5469,10 +5523,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>113</v>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>leisure</t>
@@ -5512,11 +5568,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5557,10 +5613,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>115</v>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>auto</t>
@@ -5583,12 +5641,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>XOS</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5600,10 +5658,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>116</v>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>medical</t>
@@ -5643,10 +5703,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>117</v>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>chemical</t>
@@ -5686,10 +5748,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>118</v>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>building</t>
@@ -5729,10 +5793,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>119</v>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>food/bev</t>
@@ -5772,10 +5838,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>120</v>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>energy</t>
@@ -5798,12 +5866,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5815,10 +5883,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>121</v>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>retail</t>
@@ -5858,10 +5928,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>122</v>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>food/bev</t>
@@ -5901,10 +5973,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>123</v>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>utility</t>
@@ -5927,12 +6001,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5944,10 +6018,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>124</v>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>chemical</t>
@@ -5987,10 +6063,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>125</v>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>building</t>
@@ -6030,10 +6108,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>126</v>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>software</t>
@@ -6073,10 +6153,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>127</v>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>machine</t>
@@ -6116,10 +6198,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>128</v>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>transportation</t>
@@ -6159,10 +6243,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>129</v>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -6202,10 +6288,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>130</v>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6245,10 +6333,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>131</v>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6288,10 +6378,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>132</v>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>leisure</t>
@@ -6331,10 +6423,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>133</v>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6374,10 +6468,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>134</v>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>building</t>
@@ -6417,10 +6513,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>135</v>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>leisure</t>
@@ -6460,10 +6558,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>136</v>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6486,12 +6586,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6503,10 +6603,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>137</v>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>aerospace/defense</t>
@@ -6546,10 +6648,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>138</v>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6589,10 +6693,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>139</v>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>energy</t>
@@ -6632,10 +6738,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>140</v>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>busins svc</t>
@@ -6675,10 +6783,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>141</v>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6718,10 +6828,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>142</v>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>consumer</t>
@@ -6744,12 +6856,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>FIGS</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -3988,12 +3988,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4001,44 +4001,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>XMTR</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>XMTR</t>
-        </is>
-      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4046,44 +4046,44 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>QUAD</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>QUAD</t>
-        </is>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4091,44 +4091,44 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>FRD</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -4136,44 +4136,44 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>TAL</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>TAL</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4181,44 +4181,44 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>CIX</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>CIX</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4226,44 +4226,44 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>KRT</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>KRT</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4271,44 +4271,44 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>KNBWY</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>KNBWY</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4316,44 +4316,44 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>IDT</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>IDT</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4361,44 +4361,44 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>AIRT</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>AIRT</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4406,44 +4406,44 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>JAPSY</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>JAPSY</t>
-        </is>
-      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4451,44 +4451,44 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>LITE</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4496,44 +4496,44 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>GCT</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>GCT</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4541,44 +4541,44 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>MATV</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>MATV</t>
-        </is>
-      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4586,44 +4586,44 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>LILAK</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>LILAK</t>
-        </is>
-      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4631,44 +4631,44 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>JBHT</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4676,44 +4676,44 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>PDEX</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>PDEX</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4721,44 +4721,44 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>EVVTY</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>EVVTY</t>
-        </is>
-      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4766,44 +4766,44 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>ELF</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>ELF</t>
-        </is>
-      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -4811,44 +4811,44 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>USFD</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>USFD</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -4856,44 +4856,44 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>CRS</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>CRS</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -4901,44 +4901,44 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>AER</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>AER</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -4946,44 +4946,44 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>CLH</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-clean-harbors-clh.htm</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>CLH</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4991,44 +4991,44 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>VWDRY</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>VWDRY</t>
-        </is>
-      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5036,44 +5036,44 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
           <t>BASFY</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>BASFY</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -5081,44 +5081,44 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>OESX</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>OESX</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -5126,44 +5126,44 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
           <t>ADBE</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-adobe-adbe.htm</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>ADBE</t>
-        </is>
-      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -5171,44 +5171,44 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -5216,44 +5216,44 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
           <t>AGM</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>AGM</t>
-        </is>
-      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -5261,44 +5261,44 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
           <t>MTCH</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>MTCH</t>
-        </is>
-      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -5306,44 +5306,44 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
           <t>HSTM</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-healthstream-hstm.htm</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>HSTM</t>
-        </is>
-      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5351,44 +5351,44 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
           <t>SZKMY</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>SZKMY</t>
-        </is>
-      </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -5396,44 +5396,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
           <t>TILE</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -5441,44 +5441,44 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
           <t>NUTX</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>NUTX</t>
-        </is>
-      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -5486,44 +5486,44 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
           <t>JAPAY</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>JAPAY</t>
-        </is>
-      </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -5531,44 +5531,44 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
           <t>LTH</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -5576,44 +5576,44 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
           <t>ACIW</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>ACIW</t>
-        </is>
-      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5621,44 +5621,44 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
           <t>MLR</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>MLR</t>
-        </is>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5666,44 +5666,44 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
           <t>MLAB</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>MLAB</t>
-        </is>
-      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5711,44 +5711,44 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
           <t>NVZMY</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-novonesis-adr-nvzmy.htm</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>NVZMY</t>
-        </is>
-      </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5756,44 +5756,44 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
           <t>CHCI</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>CHCI</t>
-        </is>
-      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5801,44 +5801,44 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>MAMA</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-mamas-creations-mama.htm</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>MAMA</t>
-        </is>
-      </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5846,44 +5846,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
           <t>UROY</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>UROY</t>
-        </is>
-      </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -5891,44 +5891,44 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>ANF</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>ANF</t>
-        </is>
-      </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -5936,44 +5936,44 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
           <t>SENEB</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-seneca-foods-cl-b-seneb.htm</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>SENEB</t>
-        </is>
-      </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -5981,44 +5981,44 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-excelerate-energy-ee.htm</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6026,44 +6026,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
           <t>AVNT</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>AVNT</t>
-        </is>
-      </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -6071,44 +6071,44 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>IESC</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>IESC</t>
-        </is>
-      </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -6116,44 +6116,44 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
           <t>SPSC</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sps-commerce-spsc.htm</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6161,44 +6161,44 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
           <t>SOTK</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sonotek-sotk.htm</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -6206,44 +6206,44 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6251,44 +6251,44 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
           <t>ODC</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>ODC</t>
-        </is>
-      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -6296,44 +6296,44 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
           <t>PRTS</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>PRTS</t>
-        </is>
-      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -6341,44 +6341,44 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
           <t>EAT</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>EAT</t>
-        </is>
-      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -6386,44 +6386,44 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
           <t>HTHT</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>HTHT</t>
-        </is>
-      </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -6431,44 +6431,44 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
           <t>GIC</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>GIC</t>
-        </is>
-      </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -6476,44 +6476,44 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
           <t>CPAC</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>CPAC</t>
-        </is>
-      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -6521,44 +6521,44 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
           <t>IMAX</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>IMAX</t>
-        </is>
-      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -6566,44 +6566,44 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
           <t>FIVE</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>FIVE</t>
-        </is>
-      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -6611,44 +6611,44 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
           <t>RYCEY</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-rollsroyce-holdings-adr-rycey.htm</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>RYCEY</t>
-        </is>
-      </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6656,44 +6656,44 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
           <t>SRGHY</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-shoprite-holdings-adr-srghy.htm</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>SRGHY</t>
-        </is>
-      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -6701,44 +6701,44 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
           <t>FSLR</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -6746,44 +6746,44 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
           <t>FTDR</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-frontdoor-ftdr.htm</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>FTDR</t>
-        </is>
-      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -6791,44 +6791,44 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
           <t>HZO</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>HZO</t>
-        </is>
-      </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -6836,32 +6836,32 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
           <t>JRSH</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>JRSH</t>
-        </is>
-      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -528,35 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,11 +573,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -586,22 +586,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-teekay-tankers-tnk.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,40 +663,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -708,40 +708,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -753,35 +753,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,11 +798,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -811,22 +811,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,40 +888,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,35 +1068,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,40 +1158,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,40 +1338,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apa-apa.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1383,40 +1383,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1428,35 +1428,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1473,35 +1473,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1518,35 +1518,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1563,35 +1563,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,35 +1608,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1653,35 +1653,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1711,27 +1711,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-viasat-vsat.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1756,27 +1756,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-remitly-global-rely.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1788,35 +1788,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>30</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1833,35 +1831,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permian-resources-pr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1878,35 +1876,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1923,35 +1921,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1968,35 +1966,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2013,35 +2011,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2058,35 +2056,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 35</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2103,35 +2101,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2148,35 +2146,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,35 +2191,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-business-financial-services-fbiz.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2238,35 +2236,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2283,35 +2281,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2328,40 +2326,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>WSBF</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-waterstone-financial-wsbf.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2373,35 +2371,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-bancorp-usb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2418,35 +2416,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2463,35 +2461,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2508,35 +2506,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 32</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2553,11 +2551,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2566,27 +2564,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ezcorp-cl-a-ezpw.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2598,35 +2596,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-reinsurance-group-of-america-rga.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-business-financial-services-fbiz.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,40 +2641,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-bristol-myers-squibb-bmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2686,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2701,22 +2699,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,40 +2731,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2778,40 +2776,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2823,35 +2821,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2868,35 +2866,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2913,35 +2911,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 29</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2958,40 +2956,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3003,40 +3001,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3048,35 +3046,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3093,35 +3091,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>59</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3138,35 +3134,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,35 +3179,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3228,35 +3224,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>NREF</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nexpoint-real-estate-finance-nref.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>NREF</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3273,35 +3269,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>63</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-chemed-che.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3318,35 +3312,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3363,40 +3357,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3408,35 +3402,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3453,35 +3447,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3498,35 +3492,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3543,35 +3537,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>69</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NREF</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nexpoint-real-estate-finance-nref.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NREF</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3588,35 +3580,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3633,11 +3625,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3646,27 +3638,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3678,80 +3670,80 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 23</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-merck-mrk.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3763,40 +3755,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3808,40 +3800,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,40 +3845,38 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>76</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3898,170 +3888,166 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ww-grainger-gww.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-stagwell-stgw.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>78</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CECO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ceco-environmental-ceco.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>80</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4071,222 +4057,216 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>81</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 42</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>84</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>85</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4296,727 +4276,701 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>87</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>88</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>89</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>90</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>91</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 22</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>93</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>94</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>95</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>96</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>97</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>98</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>100</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>101</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5031,9 +4985,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>102</v>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5076,9 +5028,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>103</v>
-      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5121,9 +5071,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>104</v>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5166,9 +5114,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>105</v>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5211,9 +5157,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>106</v>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5256,9 +5200,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>107</v>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5301,9 +5243,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>108</v>
-      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5346,9 +5286,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>109</v>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5391,9 +5329,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>110</v>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5436,9 +5372,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>111</v>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5481,9 +5415,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C113" t="n">
-        <v>112</v>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5526,9 +5458,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v>113</v>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5571,9 +5501,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C115" t="n">
-        <v>114</v>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5616,9 +5544,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v>115</v>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5661,9 +5587,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>116</v>
-      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5706,9 +5630,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>117</v>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5751,9 +5673,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>118</v>
-      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5796,9 +5716,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>119</v>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5841,9 +5759,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>120</v>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5886,9 +5802,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>121</v>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5931,9 +5845,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>122</v>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5976,9 +5888,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>123</v>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6021,9 +5931,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>124</v>
-      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6066,9 +5974,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>125</v>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6111,9 +6017,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>126</v>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6156,9 +6060,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>127</v>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6201,9 +6103,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>128</v>
-      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6246,9 +6146,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>129</v>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6291,9 +6189,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>130</v>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6336,9 +6232,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>131</v>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6381,9 +6275,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>132</v>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6426,9 +6318,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>133</v>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6471,9 +6361,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>134</v>
-      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6516,9 +6404,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>135</v>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6561,9 +6447,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>136</v>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6606,9 +6490,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>137</v>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6651,9 +6533,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C139" t="n">
-        <v>138</v>
-      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6696,9 +6576,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>139</v>
-      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6741,9 +6619,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>140</v>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6786,9 +6662,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>141</v>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -6831,9 +6705,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>142</v>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>N/A</t>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -528,11 +528,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -708,40 +708,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -753,35 +753,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,11 +798,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -811,22 +811,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,40 +888,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -933,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1036,22 +1036,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,40 +1068,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,35 +1158,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1216,22 +1216,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,40 +1293,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ternium-adr-tx.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1338,40 +1338,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apa-apa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1383,40 +1383,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1473,35 +1473,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1563,35 +1563,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,40 +1608,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1653,35 +1653,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1698,40 +1698,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-viasat-vsat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1743,40 +1743,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1788,33 +1788,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>▲ 13</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>43</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1831,11 +1833,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1876,35 +1878,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1921,35 +1923,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1966,40 +1968,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>TECK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-teck-resources-cl-b-teck.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2011,40 +2013,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2056,35 +2058,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 35</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2101,35 +2103,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2146,35 +2148,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2191,35 +2193,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2236,35 +2238,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2281,35 +2283,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2326,40 +2328,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WSBF</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-waterstone-financial-wsbf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2371,11 +2373,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2384,27 +2386,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>CQP</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cheniere-energy-partners-cqp.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2416,35 +2418,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2461,35 +2463,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2506,35 +2508,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 32</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2551,40 +2553,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ezcorp-cl-a-ezpw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-viasat-vsat.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2596,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-business-financial-services-fbiz.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2641,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2686,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2731,40 +2733,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2776,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lake-shore-bancorp-lsbk.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>WSBF</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2821,35 +2823,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ezcorp-cl-a-ezpw.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2866,11 +2868,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2884,22 +2886,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>EJPRY</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>UNP</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2911,11 +2913,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2951,130 +2953,130 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 29</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3086,83 +3088,85 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>▲ 5</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>65</v>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>JXN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jackson-financial-jxn.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3174,40 +3178,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3219,40 +3223,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NREF</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nexpoint-real-estate-finance-nref.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>NREF</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3264,83 +3268,85 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>▼ 4</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>62</v>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>NREF</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3352,130 +3358,130 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3487,40 +3493,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▼ 23</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3532,1445 +3538,1485 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>69</v>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>FRD</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>FRD</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>LQDT</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>LQDT</t>
-        </is>
-      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>WPM</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>NEM</t>
-        </is>
-      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>MRK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-merck-mrk.htm</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>BMY</t>
-        </is>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>MTLS</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>MTLS</t>
-        </is>
-      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>CXW</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>CXW</t>
-        </is>
-      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>CAH</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>CAH</t>
-        </is>
-      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>77</v>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>IDT</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>IDT</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>STGW</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-stagwell-stgw.htm</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>MGNI</t>
-        </is>
-      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>80</v>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>CECO</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ceco-environmental-ceco.htm</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>CLH</t>
-        </is>
-      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>CPAY</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>82</v>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>QUAD</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>QUAD</t>
-        </is>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>83</v>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>VWDRY</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>VWDRY</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>EXPE</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>CAAS</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>CAAS</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>86</v>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>CIX</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>CIX</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>87</v>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>KNBWY</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>KNBWY</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>ULTA</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>GWW</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>89</v>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>USFD</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>USFD</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>90</v>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>JBHT</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>JBHT</t>
-        </is>
-      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>91</v>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>TAL</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>TAL</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>93</v>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>ELF</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>ELF</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>95</v>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>AER</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>AER</t>
-        </is>
-      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>ESCA</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>ESCA</t>
-        </is>
-      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>98</v>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>KRT</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>KRT</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>99</v>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>MATV</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>MATV</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>100</v>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>CRS</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>CRS</t>
-        </is>
-      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>101</v>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>GCT</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>GCT</t>
-        </is>
-      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>102</v>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>EVVTY</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>EVVTY</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>103</v>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>JAPSY</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>JAPSY</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>NIQ</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>FDS</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>108</v>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
           <t>AIRT</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>AIRT</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>116</v>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>PDEX</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>PDEX</t>
-        </is>
-      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -478,40 +478,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -523,40 +523,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,16 +568,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -586,22 +586,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -613,85 +613,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fortinet-ftnt.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -703,40 +703,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,40 +748,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -793,61 +793,61 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>OOMA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -856,43 +856,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>VIST</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-vista-energy-adr-vist.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,22 +901,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -928,40 +928,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -973,40 +973,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1018,16 +1018,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1036,22 +1036,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1063,220 +1063,220 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-bgc-group-cl-a-bgc.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gerdau-adr-ggb.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1288,130 +1288,130 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ternium-adr-tx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1423,40 +1423,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1468,40 +1468,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1513,85 +1513,85 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carvana-cl-a-cvna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1603,175 +1603,175 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pjt-partners-pjt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1783,40 +1783,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1828,40 +1828,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1873,40 +1873,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ooma-ooma.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1918,57 +1918,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1976,48 +1976,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TECK</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-teck-resources-cl-b-teck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2026,67 +2026,67 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2098,85 +2098,85 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>WSBF</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-waterstone-financial-wsbf.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,40 +2188,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,40 +2233,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2278,175 +2278,175 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-openlane-opln.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CQP</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cheniere-energy-partners-cqp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-viasat-vsat.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2458,40 +2458,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2503,40 +2503,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ezcorp-cl-a-ezpw.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2548,16 +2548,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2566,22 +2566,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-viasat-vsat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2593,40 +2593,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>JXN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jackson-financial-jxn.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>JXN</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2638,220 +2638,218 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CQP</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 5</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>56</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lake-shore-bancorp-lsbk.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WSBF</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ezcorp-cl-a-ezpw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2863,85 +2861,85 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2953,16 +2951,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2998,40 +2996,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3043,130 +3041,128 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JXN</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jackson-financial-jxn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 3</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>58</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3178,40 +3174,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3228,35 +3224,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 1</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>66</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3273,40 +3267,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 31</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NREF</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3318,40 +3312,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>TECK</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3363,40 +3357,38 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>68</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3408,35 +3400,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 7</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>63</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3453,35 +3443,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▼ 10</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>61</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3493,40 +3481,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3538,1485 +3526,1427 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>69</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>70</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>71</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>74</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>75</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>76</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>77</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-clean-harbors-clh.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>CECO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SANM</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sanmina-sanm.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CECO</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>81</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>82</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>83</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>84</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>85</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>86</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>87</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>88</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>89</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>90</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>91</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 32</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>95</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>96</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>98</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>99</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>100</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>101</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>102</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dexcom-dxcm.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>103</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>106</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>108</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>116</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5031,7 +4961,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5054,7 +4986,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5074,7 +5006,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -5097,7 +5031,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -478,40 +478,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -523,40 +521,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,12 +566,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -613,52 +611,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fortinet-ftnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -667,31 +665,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -703,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -712,31 +710,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,40 +746,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>9</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -793,16 +789,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -826,52 +822,52 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OOMA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VIST</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-vista-energy-adr-vist.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-sumitomo-mitsui-trust-group-adr-sutny.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -883,16 +879,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -906,62 +902,62 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -973,40 +969,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1018,7 +1014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1027,7 +1023,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1036,43 +1032,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1081,22 +1077,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1108,85 +1104,85 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-bgc-group-cl-a-bgc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1198,40 +1194,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gerdau-adr-ggb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1243,16 +1239,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1288,16 +1284,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1333,106 +1329,106 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gerdau-adr-ggb.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>VIST</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1441,22 +1437,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-concentra-group-holdings-parent-con.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1468,40 +1464,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-bgc-group-cl-a-bgc.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1513,85 +1509,85 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1603,40 +1599,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,175 +1644,175 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1828,85 +1824,85 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1918,40 +1914,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1963,40 +1959,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2008,85 +2004,85 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2098,85 +2094,85 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSBF</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-waterstone-financial-wsbf.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,40 +2184,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,220 +2229,220 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-openlane-opln.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-viasat-vsat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2458,40 +2454,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2503,130 +2499,130 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ezcorp-cl-a-ezpw.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>JXN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>WSBF</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JXN</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jackson-financial-jxn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>JXN</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2638,40 +2634,38 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 8</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>59</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2683,16 +2677,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2701,65 +2695,67 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CQP</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>▼ 8</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>43</v>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ACVA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-acv-auctions-acva.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2771,40 +2767,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2816,40 +2812,40 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2861,12 +2857,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2874,72 +2870,72 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2951,40 +2947,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2996,40 +2992,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3041,40 +3037,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 25</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>SANM</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3086,40 +3082,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 30</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3131,38 +3127,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>▼ 27</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>33</v>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cardinal-health-cah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3174,40 +3172,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3219,38 +3217,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>▼ 9</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>53</v>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3262,214 +3262,220 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 31</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>TECK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>▼ 4</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>61</v>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>▲ 8</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>74</v>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>▲ 13</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>80</v>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3481,40 +3487,38 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 1</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>71</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3526,81 +3530,85 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>▼ 2</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>67</v>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>▼ 8</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>62</v>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3612,38 +3620,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>▲ 18</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>89</v>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3655,40 +3665,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3700,38 +3710,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>▼ 7</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>66</v>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3743,38 +3755,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>▼ 6</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>68</v>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3786,126 +3800,130 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>▼ 12</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>63</v>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>▲ 22</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>98</v>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-clean-harbors-clh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CECO</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3917,169 +3935,175 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sanmina-sanm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>▲ 2</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>81</v>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>▼ 4</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>76</v>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>▼ 3</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>78</v>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4091,38 +4115,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>▲ 3</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>85</v>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4134,7 +4160,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4145,27 +4171,27 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4177,38 +4203,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>▲ 2</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>86</v>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4220,38 +4248,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>▼ 12</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>73</v>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4263,7 +4293,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4274,113 +4304,117 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>▲ 16</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>103</v>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>▼ 13</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>75</v>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4392,7 +4426,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4403,27 +4437,27 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4435,40 +4469,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 32</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4480,38 +4514,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>▼ 3</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>88</v>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4523,38 +4559,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>▼ 15</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>77</v>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4566,38 +4604,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>▲ 7</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>100</v>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4609,38 +4649,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>▼ 2</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>92</v>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4652,38 +4694,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>▼ 4</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>91</v>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4695,7 +4739,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4706,39 +4750,39 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4749,27 +4793,27 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dexcom-dxcm.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>MAMA</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4781,38 +4825,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>▲ 12</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>110</v>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4824,38 +4870,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>▲ 6</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>105</v>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4867,38 +4915,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>▼ 3</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>97</v>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4910,38 +4960,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>▼ 6</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>95</v>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4953,596 +5005,608 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>▲ 4</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>108</v>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>▲ 9</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>114</v>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>▲ 6</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>112</v>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-comfort-systems-usa-fix.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>▼ 10</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>99</v>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>▲ 6</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>116</v>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>▲ 7</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>118</v>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>▼ 22</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>90</v>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5552,1115 +5616,1117 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>SENEB</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>NVZMY</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>▼ 8</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>111</v>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>MAMA</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>SENEB</t>
+          <t>NVZMY</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>RYCEY</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-mega-fortune-mgrt.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>RYCEY</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SRGHY</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>SRGHY</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6670,40 +6736,40 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6713,7 +6779,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,10 +483,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>energy</t>
@@ -571,11 +573,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -616,11 +618,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -661,11 +663,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -751,10 +753,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>computer</t>
@@ -794,11 +798,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -839,11 +843,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -867,12 +871,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -884,11 +888,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -912,12 +916,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -929,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -974,11 +978,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1019,11 +1023,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1047,12 +1051,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1109,11 +1113,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1154,11 +1158,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1199,11 +1203,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1227,12 +1231,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1244,11 +1248,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1289,11 +1293,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1334,11 +1338,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1379,11 +1383,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1407,12 +1411,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>VIST</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1424,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1469,11 +1473,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1514,11 +1518,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1559,11 +1563,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1604,11 +1608,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1649,11 +1653,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1694,11 +1698,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1739,11 +1743,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1767,12 +1771,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1784,11 +1788,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1829,11 +1833,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1857,12 +1861,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1874,11 +1878,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1919,11 +1923,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1947,12 +1951,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1964,11 +1968,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2009,11 +2013,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2037,12 +2041,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2054,11 +2058,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2099,11 +2103,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2144,11 +2148,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2189,11 +2193,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2234,11 +2238,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2262,12 +2266,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2279,11 +2283,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2324,11 +2328,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2369,11 +2373,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2397,12 +2401,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2414,11 +2418,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2459,11 +2463,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2504,11 +2508,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2532,12 +2536,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>JXN</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2549,11 +2553,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2577,12 +2581,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WSBF</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2594,11 +2598,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2639,10 +2643,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>49</v>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>alcohl/tob/thc</t>
@@ -2682,11 +2688,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2727,11 +2733,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2755,12 +2761,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>ACVA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2772,11 +2778,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2817,11 +2823,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2862,11 +2868,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2890,12 +2896,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2907,11 +2913,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2952,11 +2958,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2997,11 +3003,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3042,11 +3048,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3070,12 +3076,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3087,11 +3093,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3132,11 +3138,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3177,11 +3183,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3222,11 +3228,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3267,11 +3273,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3295,12 +3301,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3312,11 +3318,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3357,11 +3363,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3402,11 +3408,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3447,11 +3453,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3492,10 +3498,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>68</v>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>medical</t>
@@ -3535,11 +3543,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3580,11 +3588,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3625,11 +3633,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3715,11 +3723,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3760,11 +3768,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3788,12 +3796,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3805,11 +3813,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3833,12 +3841,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3858,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3895,11 +3903,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3935,40 +3943,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3980,85 +3988,85 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4070,40 +4078,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4115,40 +4123,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4160,38 +4168,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>84</v>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4203,40 +4213,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4248,40 +4258,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4293,15 +4303,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>87</v>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>machine</t>
@@ -4309,112 +4321,112 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4426,38 +4438,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>90</v>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4469,40 +4483,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4514,40 +4528,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4559,40 +4573,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4604,40 +4618,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4649,40 +4663,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4694,40 +4708,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4739,126 +4753,130 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>97</v>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>98</v>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>MAMA</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4870,40 +4888,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4915,40 +4933,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4960,40 +4978,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5005,38 +5023,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>103</v>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5048,40 +5068,40 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5093,40 +5113,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5138,40 +5158,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5183,40 +5203,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5228,15 +5248,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>108</v>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>building</t>
@@ -5244,22 +5266,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-comfort-systems-usa-fix.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5271,83 +5293,85 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>109</v>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-comfort-systems-usa-fix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5359,40 +5383,40 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5404,40 +5428,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5449,40 +5473,40 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▼ 22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5494,124 +5518,130 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>114</v>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>115</v>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>116</v>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5623,81 +5653,85 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>117</v>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>SENEB</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>118</v>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5709,38 +5743,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>119</v>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5752,126 +5788,130 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>121</v>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>122</v>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5883,15 +5923,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>123</v>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>chemical</t>
@@ -5899,65 +5941,67 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>NVZMY</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>124</v>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5969,38 +6013,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>125</v>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6012,15 +6058,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>126</v>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>leisure</t>
@@ -6028,22 +6076,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6055,38 +6103,40 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>127</v>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6098,38 +6148,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>128</v>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6141,38 +6193,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>129</v>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6184,38 +6238,40 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>130</v>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6227,38 +6283,40 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>131</v>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6270,58 +6328,62 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>132</v>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>RYCEY</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>133</v>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6329,22 +6391,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6356,15 +6418,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>134</v>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6372,22 +6436,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6399,38 +6463,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>135</v>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6442,81 +6508,85 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>136</v>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>137</v>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-mega-fortune-mgrt.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6528,81 +6598,85 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>138</v>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-mega-fortune-mgrt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>139</v>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6614,58 +6688,62 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>140</v>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>141</v>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>retail</t>
@@ -6673,65 +6751,67 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SRGHY</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>142</v>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6743,43 +6823,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>78</v>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
